--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0027.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0027.xlsx
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Ba bản Ragunnesi mỗi người à? Ta nghi ngờ là bên đó có bán được nhiều pizza như thế không...</t>
+          <t>Ba bản Ragunnesi mỗi người à? Tao nghi ngờ là bên đó có bán được nhiều pizza như thế không...</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Ta nghe nói ngươi đang tuyển cố vấn à?</t>
+          <t>Tao nghe nói mày đang tuyển cố vấn à?</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>*sigh*...</t>
+          <t>Thở dài...</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>À, cái đó... Dạo này ta mới nhận một dự án hàng hóa từ chi nhánh Ragunna ở Rinascita.</t>
+          <t>À, cái đó... Dạo này tao mới nhận một dự án hàng hóa từ chi nhánh Ragunna ở Rinascita.</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Tôi nghĩ họ sẽ thấy hứng thú với những thiết kế ngoài nền văn hóa của mình, nên tôi đến Kim Châu để tìm cảm hứng.</t>
+          <t>Tôi nghĩ họ sẽ thấy hứng thú với những thiết kế ngoài nền văn hóa của mình, nên tôi đến Jinzhou để tìm cảm hứng.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Xin chào, chào mừng đến với Kim Châu.</t>
+          <t>Xin chào, chào mừng đến với Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả không thể sống thiếu chúng đâu.</t>
+          <t>Resonator không thể sống thiếu chúng đâu.</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Ôi trời... Ta đã cố hết sức rồi. Liệu ta có bán được món hàng này không đây?</t>
+          <t>Ôi trời... Tao đã cố hết sức rồi. Liệu tao có bán được món hàng này không đây?</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>{PlayerName} à, ta không ngờ cậu lại là chuyên gia sửa xe tự động! Thế cậu biết rõ từng con ốc, từng con vít trong chiếc xe tải đó chứ?</t>
+          <t>{PlayerName} à, tao không ngờ cậu lại là chuyên gia sửa xe tự động! Thế cậu biết rõ từng con ốc, từng con vít trong chiếc xe tải đó chứ?</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Cậu chắc không?</t>
+          <t>bạn chắc không?</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Còn Echo, chúng chủ yếu phục vụ mục đích tiện ích. Các Cộng Hưởng Giả đánh bại Tổ Tacet và biến chúng thành Echo để tăng cường khả năng của mình.</t>
+          <t>Còn Echo, chúng chủ yếu phục vụ mục đích tiện ích. Các Resonator đánh bại Tổ Tacet và biến chúng thành Echo để tăng cường khả năng của mình.</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Sau bao công sức, Alannah cũng gửi được một lô thú nhồi bông Echo phong cách Kim Châu đến Ragunna.</t>
+          <t>Sau bao công sức, Alannah cũng gửi được một lô thú nhồi bông Echo phong cách Jinzhou đến Ragunna.</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Lần tới có gì ta lại nhắn ngươi ngay! Cảm ơn vì đã ghé qua hôm nay, {PlayerName}!</t>
+          <t>Lần tới có gì tao lại nhắn mày ngay! Cảm ơn vì đã ghé qua hôm nay, {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ví dụ, hồi ta kể về Carnevale là ngươi dính như đỉa phải!</t>
+          <t>Ví dụ, hồi tao kể về Carnevale là mày dính như đỉa phải!</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Nếu cậu không ở bên ta đến phút cuối, có lẽ ta đã sụp đổ từ lâu rồi...</t>
+          <t>Nếu cậu không ở bên tao đến phút cuối, có lẽ tao đã sụp đổ từ lâu rồi...</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Hãy khiến chúng ta phải trầm trồ đi, kẻ giàu nhất ở Kim Châu.</t>
+          <t>Hãy khiến chúng ta phải trầm trồ đi, kẻ giàu nhất ở Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Mahe bảo ông không phải là người giàu nhất Kim Châu. Ừ thì...</t>
+          <t>Mahe bảo ông không phải là người giàu nhất Jinzhou. Ừ thì...</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Khi nào ta có đủ thông tin chi tiết này, Ragunna sẽ phải choáng váng!</t>
+          <t>Khi nào tao có đủ thông tin chi tiết này, Ragunna sẽ phải choáng váng!</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Những thứ như này có thể là điều phi thường đối với người Ragunnesi. Ta đang nghĩ là... có lẽ...</t>
+          <t>Những thứ như này có thể là điều phi thường đối với người Ragunnesi. Tao đang nghĩ là... có lẽ...</t>
         </is>
       </c>
     </row>
